--- a/01_analyses_full/results/SoIB_summaries.xlsx
+++ b/01_analyses_full/results/SoIB_summaries.xlsx
@@ -11,25 +11,222 @@
     <sheet name="Range Status" sheetId="2" r:id="rId2"/>
     <sheet name="Priority Status" sheetId="3" r:id="rId3"/>
     <sheet name="Species qualification" sheetId="4" r:id="rId4"/>
-    <sheet name="Interannual update - High Pr" sheetId="5" r:id="rId5"/>
-    <sheet name="SoIB major vs interannual up" sheetId="6" r:id="rId6"/>
-    <sheet name="SoIB interannual vs major up" sheetId="7" r:id="rId7"/>
-    <sheet name="SoIB interannual update vs I" sheetId="8" r:id="rId8"/>
-    <sheet name="SoIB interannual update vs I_1" sheetId="9" r:id="rId9"/>
-    <sheet name="SoIB interannual update vs I_2" sheetId="10" r:id="rId10"/>
-    <sheet name="Interannual update - Reason " sheetId="11" r:id="rId11"/>
-    <sheet name="Interannual update - Reason _1" sheetId="12" r:id="rId12"/>
-    <sheet name="Major update - High Priority" sheetId="13" r:id="rId13"/>
+    <sheet name="Interannual update - High Prior" sheetId="5" r:id="rId5"/>
+    <sheet name="SoIB major vs interannual updat" sheetId="6" r:id="rId6"/>
+    <sheet name="SoIB interannual vs major updat" sheetId="7" r:id="rId7"/>
+    <sheet name="SoIB interannual update vs IUCN" sheetId="8" r:id="rId8"/>
+    <sheet name="SoIB interannual update vs IU_1" sheetId="9" r:id="rId9"/>
+    <sheet name="SoIB interannual update vs IU_2" sheetId="10" r:id="rId10"/>
+    <sheet name="Interannual update - Reason for" sheetId="11" r:id="rId11"/>
+    <sheet name="Interannual update - Reason f_1" sheetId="12" r:id="rId12"/>
+    <sheet name="Major update - High Priority br" sheetId="13" r:id="rId13"/>
     <sheet name="SoIB past vs major update" sheetId="14" r:id="rId14"/>
     <sheet name="SoIB major update vs past" sheetId="15" r:id="rId15"/>
-    <sheet name="SoIB major update vs IUCN (n" sheetId="16" r:id="rId16"/>
-    <sheet name="SoIB major update vs IUCN (I" sheetId="17" r:id="rId17"/>
-    <sheet name="SoIB major update vs IUCN (S" sheetId="18" r:id="rId18"/>
-    <sheet name="Major update - Reason for up" sheetId="19" r:id="rId19"/>
-    <sheet name="Major update - Reason for do" sheetId="20" r:id="rId20"/>
+    <sheet name="SoIB major update vs IUCN (no.)" sheetId="16" r:id="rId16"/>
+    <sheet name="SoIB major update vs IUCN (IUCN" sheetId="17" r:id="rId17"/>
+    <sheet name="SoIB major update vs IUCN (SoIB" sheetId="18" r:id="rId18"/>
+    <sheet name="Major update - Reason for uplis" sheetId="19" r:id="rId19"/>
+    <sheet name="Major update - Reason for downl" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="64">
+  <si>
+    <t>Trend Status</t>
+  </si>
+  <si>
+    <t>Long-term species (no.)</t>
+  </si>
+  <si>
+    <t>Current species (no.)</t>
+  </si>
+  <si>
+    <t>Long-term species conclusive (perc.)</t>
+  </si>
+  <si>
+    <t>Current species conclusive (perc.)</t>
+  </si>
+  <si>
+    <t>Rapid Decline</t>
+  </si>
+  <si>
+    <t>Decline</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Rapid Increase</t>
+  </si>
+  <si>
+    <t>Trend Inconclusive</t>
+  </si>
+  <si>
+    <t>Insufficient Data</t>
+  </si>
+  <si>
+    <t>Range Status</t>
+  </si>
+  <si>
+    <t>Species (no.)</t>
+  </si>
+  <si>
+    <t>Species (perc.)</t>
+  </si>
+  <si>
+    <t>Historical</t>
+  </si>
+  <si>
+    <t>Very Restricted</t>
+  </si>
+  <si>
+    <t>Restricted</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Very Large</t>
+  </si>
+  <si>
+    <t>Priority Status</t>
+  </si>
+  <si>
+    <t>No. of species</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>No. of species in:</t>
+  </si>
+  <si>
+    <t>Selected for analysis</t>
+  </si>
+  <si>
+    <t>With conclusive trends</t>
+  </si>
+  <si>
+    <t>SoIB Assessment</t>
+  </si>
+  <si>
+    <t>Long-term Analysis</t>
+  </si>
+  <si>
+    <t>Current Analysis</t>
+  </si>
+  <si>
+    <t>Range Analysis</t>
+  </si>
+  <si>
+    <t>Break-up</t>
+  </si>
+  <si>
+    <t>High Species (no.)</t>
+  </si>
+  <si>
+    <t>High Species (perc.)</t>
+  </si>
+  <si>
+    <t>New High Species (no.)</t>
+  </si>
+  <si>
+    <t>New High Species (perc.)</t>
+  </si>
+  <si>
+    <t>Trend New</t>
+  </si>
+  <si>
+    <t>Trend Different</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>IUCN</t>
+  </si>
+  <si>
+    <t>SoIB Major Update Priority Status</t>
+  </si>
+  <si>
+    <t>SoIB Latest Priority Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Critically Endangered</t>
+  </si>
+  <si>
+    <t>Endangered</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>Near Threatened</t>
+  </si>
+  <si>
+    <t>Least Concern</t>
+  </si>
+  <si>
+    <t>Not recognized</t>
+  </si>
+  <si>
+    <t>More decline in LTT</t>
+  </si>
+  <si>
+    <t>More decline in CAT</t>
+  </si>
+  <si>
+    <t>First-time trend</t>
+  </si>
+  <si>
+    <t>First-time LTT</t>
+  </si>
+  <si>
+    <t>First-time CAT</t>
+  </si>
+  <si>
+    <t>Other changes in trends</t>
+  </si>
+  <si>
+    <t>Loss of trends</t>
+  </si>
+  <si>
+    <t>Reducing range</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Less decline in LTT</t>
+  </si>
+  <si>
+    <t>Less decline in CAT</t>
+  </si>
+  <si>
+    <t>Increasing range</t>
+  </si>
+  <si>
+    <t>SoIB Past Priority Status</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -373,146 +570,122 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Trend Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Long-term species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Current species (no.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Long-term species conclusive (perc.)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Current species conclusive (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rapid Decline</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>118</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>34.5</v>
       </c>
       <c r="E2">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Decline</t>
-        </is>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
       </c>
       <c r="B3">
         <v>109</v>
       </c>
       <c r="C3">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D3">
         <v>31.9</v>
       </c>
       <c r="E3">
-        <v>26.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
         <v>61</v>
       </c>
       <c r="C4">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D4">
         <v>17.8</v>
       </c>
       <c r="E4">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Increase</t>
-        </is>
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
       <c r="B5">
         <v>26</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>7.6</v>
       </c>
       <c r="E5">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rapid Increase</t>
-        </is>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
       </c>
       <c r="B6">
         <v>28</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>8.199999999999999</v>
       </c>
       <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Trend Inconclusive</t>
-        </is>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="B7">
         <v>183</v>
       </c>
       <c r="C7">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Insufficient Data</t>
-        </is>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
         <v>406</v>
@@ -531,116 +704,96 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="C2">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="D2">
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
       <c r="E2">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>35.8</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0.8</v>
       </c>
       <c r="C3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
       <c r="F3">
-        <v>82.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0.7</v>
       </c>
       <c r="E4">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="F4">
-        <v>96.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="G4">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -653,93 +806,75 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>More decline in LTT</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>51</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>More decline in CAT</t>
-        </is>
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>52</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>First-time trend</t>
-        </is>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>53</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>First-time LTT</t>
-        </is>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>54</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>First-time CAT</t>
-        </is>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>55</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Other changes in trends</t>
-        </is>
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>56</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -748,11 +883,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loss of trends</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>57</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -761,30 +894,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Reducing range</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>58</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>59</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
@@ -797,54 +926,42 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Less decline in LTT</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>60</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Less decline in CAT</t>
-        </is>
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>61</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>First-time trend</t>
-        </is>
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>53</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -853,11 +970,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>First-time LTT</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>54</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -866,69 +981,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>First-time CAT</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>55</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Other changes in trends</t>
-        </is>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>56</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loss of trends</t>
-        </is>
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>57</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Increasing range</t>
-        </is>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>62</v>
       </c>
       <c r="B9">
         <v>13</v>
       </c>
       <c r="C9">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>59</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -941,38 +1046,26 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>High Species (perc.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>New High Species (no.)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>New High Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Trend New</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>37</v>
       </c>
       <c r="B2">
         <v>77</v>
@@ -987,11 +1080,9 @@
         <v>68.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trend Different</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>38</v>
       </c>
       <c r="B3">
         <v>17</v>
@@ -1006,11 +1097,9 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>39</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -1025,11 +1114,9 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IUCN</t>
-        </is>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>40</v>
       </c>
       <c r="B5">
         <v>39</v>
@@ -1054,38 +1141,26 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Past Priority Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Major Update Priority Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
       <c r="C2">
         <v>74</v>
@@ -1094,16 +1169,12 @@
         <v>73.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1112,16 +1183,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -1130,11 +1197,9 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>23</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -1143,16 +1208,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -1161,16 +1222,12 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
         <v>333</v>
@@ -1179,16 +1236,12 @@
         <v>75.7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
       </c>
       <c r="C8">
         <v>71</v>
@@ -1197,11 +1250,9 @@
         <v>16.1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1210,16 +1261,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
       </c>
       <c r="C10">
         <v>56</v>
@@ -1228,16 +1275,12 @@
         <v>17.6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
       </c>
       <c r="C11">
         <v>81</v>
@@ -1246,16 +1289,12 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12">
         <v>166</v>
@@ -1264,11 +1303,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -1287,38 +1324,26 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Major Update Priority Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Past Priority Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
       <c r="C2">
         <v>74</v>
@@ -1327,16 +1352,12 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3">
         <v>32</v>
@@ -1345,16 +1366,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
       </c>
       <c r="C4">
         <v>56</v>
@@ -1363,11 +1380,9 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>23</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -1376,16 +1391,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -1394,16 +1405,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
         <v>333</v>
@@ -1412,16 +1419,12 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
       </c>
       <c r="C8">
         <v>81</v>
@@ -1430,11 +1433,9 @@
         <v>18.4</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -1443,16 +1444,12 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
       </c>
       <c r="C10">
         <v>22</v>
@@ -1461,16 +1458,12 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
       </c>
       <c r="C11">
         <v>71</v>
@@ -1479,16 +1472,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12">
         <v>166</v>
@@ -1497,11 +1486,9 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>64</v>
@@ -1520,38 +1507,26 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>45</v>
       </c>
       <c r="B2">
         <v>16</v>
@@ -1566,11 +1541,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>46</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -1585,11 +1558,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>47</v>
       </c>
       <c r="B4">
         <v>35</v>
@@ -1604,11 +1575,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>48</v>
       </c>
       <c r="B5">
         <v>28</v>
@@ -1623,11 +1592,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>49</v>
       </c>
       <c r="B6">
         <v>87</v>
@@ -1642,11 +1609,9 @@
         <v>777</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1661,11 +1626,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>44</v>
       </c>
       <c r="B8">
         <v>177</v>
@@ -1690,33 +1653,23 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>45</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1728,11 +1681,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>46</v>
       </c>
       <c r="B3">
         <v>84.59999999999999</v>
@@ -1744,11 +1695,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>47</v>
       </c>
       <c r="B4">
         <v>85.40000000000001</v>
@@ -1760,11 +1709,9 @@
         <v>4.9</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>48</v>
       </c>
       <c r="B5">
         <v>39.4</v>
@@ -1776,11 +1723,9 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>49</v>
       </c>
       <c r="B6">
         <v>11.2</v>
@@ -1792,11 +1737,9 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1818,48 +1761,32 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -1880,11 +1807,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1905,11 +1830,9 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1940,28 +1863,20 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>More decline in LTT</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>51</v>
       </c>
       <c r="B2">
         <v>22</v>
@@ -1970,11 +1885,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>More decline in CAT</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>52</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1983,11 +1896,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>First-time trend</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>53</v>
       </c>
       <c r="B4">
         <v>32</v>
@@ -1996,11 +1907,9 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>First-time LTT</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>54</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -2009,11 +1918,9 @@
         <v>2.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>First-time CAT</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>55</v>
       </c>
       <c r="B6">
         <v>20</v>
@@ -2022,11 +1929,9 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Other changes in trends</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>56</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2035,11 +1940,9 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loss of trends</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>57</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2048,11 +1951,9 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Reducing range</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>58</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -2061,11 +1962,9 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>59</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2084,28 +1983,20 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Range Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>15</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -2114,11 +2005,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Very Restricted</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>16</v>
       </c>
       <c r="B3">
         <v>36</v>
@@ -2127,11 +2016,9 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Restricted</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>17</v>
       </c>
       <c r="B4">
         <v>195</v>
@@ -2140,11 +2027,9 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>18</v>
       </c>
       <c r="B5">
         <v>360</v>
@@ -2153,11 +2038,9 @@
         <v>38.7</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>19</v>
       </c>
       <c r="B6">
         <v>189</v>
@@ -2166,11 +2049,9 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Very Large</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>20</v>
       </c>
       <c r="B7">
         <v>148</v>
@@ -2189,28 +2070,20 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Less decline in LTT</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>60</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2219,11 +2092,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Less decline in CAT</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>61</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -2232,11 +2103,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>First-time trend</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>53</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2245,11 +2114,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>First-time LTT</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>54</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2258,11 +2125,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>First-time CAT</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>55</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2271,11 +2136,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Other changes in trends</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>56</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2284,11 +2147,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loss of trends</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>57</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -2297,11 +2158,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Increasing range</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>62</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2310,11 +2169,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>59</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -2333,46 +2190,36 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Priority Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>No. of species</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -2385,38 +2232,28 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No. of species in:</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Selected for analysis</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>With conclusive trends</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SoIB Assessment</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>28</v>
       </c>
       <c r="B2">
         <v>931</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Long-term Analysis</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>29</v>
       </c>
       <c r="B3">
         <v>525</v>
@@ -2425,24 +2262,20 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Current Analysis</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>30</v>
       </c>
       <c r="B4">
         <v>644</v>
       </c>
       <c r="C4">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Range Analysis</t>
-        </is>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>31</v>
       </c>
       <c r="B5">
         <v>931</v>
@@ -2458,79 +2291,63 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Break-up</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High Species (no.)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>High Species (perc.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>New High Species (no.)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>New High Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Trend New</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>12.6</v>
+        <v>10.4</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>58.8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trend Different</t>
-        </is>
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>18.4</v>
+        <v>22.6</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>34</v>
@@ -2539,26 +2356,24 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IUCN</t>
-        </is>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
@@ -2571,87 +2386,65 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Major Update Priority Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Latest Priority Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D2">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D4">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>23</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2660,65 +2453,51 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D7">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D8">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -2727,65 +2506,51 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D11">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D12">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -2804,188 +2569,144 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Latest Priority Status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SoIB Major Update Priority Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species (no.)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Species (perc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D2">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D6">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
       </c>
       <c r="C7">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>80</v>
+      </c>
+      <c r="D8">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
         <v>66</v>
       </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>85</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>63</v>
-      </c>
       <c r="D9">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D10">
-        <v>61.8</v>
+        <v>62.8</v>
       </c>
     </row>
   </sheetData>
@@ -2998,38 +2719,26 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>45</v>
       </c>
       <c r="B2">
         <v>13</v>
@@ -3044,30 +2753,26 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>46</v>
       </c>
       <c r="B3">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>47</v>
       </c>
       <c r="B4">
         <v>30</v>
@@ -3082,49 +2787,43 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>48</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>71</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>49</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>319</v>
       </c>
       <c r="D6">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E6">
         <v>777</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3139,20 +2838,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>44</v>
       </c>
       <c r="B8">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C8">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D8">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E8">
         <v>931</v>
@@ -3168,33 +2865,23 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Critically Endangered</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>45</v>
       </c>
       <c r="B2">
         <v>81.2</v>
@@ -3206,27 +2893,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Endangered</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>46</v>
       </c>
       <c r="B3">
         <v>84.59999999999999</v>
       </c>
       <c r="C3">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="D3">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vulnerable</t>
-        </is>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>47</v>
       </c>
       <c r="B4">
         <v>73.2</v>
@@ -3238,43 +2921,37 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Near Threatened</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>48</v>
       </c>
       <c r="B5">
-        <v>21.1</v>
+        <v>19.7</v>
       </c>
       <c r="C5">
-        <v>67.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="D5">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Least Concern</t>
-        </is>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>49</v>
       </c>
       <c r="B6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="C6">
         <v>41.1</v>
       </c>
       <c r="D6">
-        <v>54.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Not recognized</t>
-        </is>
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0</v>

--- a/01_analyses_full/results/SoIB_summaries.xlsx
+++ b/01_analyses_full/results/SoIB_summaries.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Trend Status</t>
   </si>
@@ -592,16 +592,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="E2">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -609,16 +609,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>91</v>
       </c>
       <c r="D3">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E3">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -626,16 +626,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D4">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="E4">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -649,10 +649,10 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="E5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -666,7 +666,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -677,10 +677,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C7">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -688,10 +688,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C8">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -732,19 +732,19 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="C2">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D2">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F2">
-        <v>35.8</v>
+        <v>35.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -764,13 +764,13 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="F3">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -787,13 +787,13 @@
         <v>0.7</v>
       </c>
       <c r="E4">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F4">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="G4">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1572,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1600,13 +1600,13 @@
         <v>87</v>
       </c>
       <c r="C6">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D6">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E6">
-        <v>777</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1620,10 +1620,10 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1631,16 +1631,16 @@
         <v>44</v>
       </c>
       <c r="B8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D8">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E8">
-        <v>931</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -1700,13 +1700,13 @@
         <v>47</v>
       </c>
       <c r="B4">
-        <v>85.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="C4">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1728,13 +1728,13 @@
         <v>49</v>
       </c>
       <c r="B6">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="C6">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="D6">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1745,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>61.5</v>
+        <v>53.3</v>
       </c>
       <c r="D7">
-        <v>38.5</v>
+        <v>46.7</v>
       </c>
     </row>
   </sheetData>
@@ -1795,13 +1795,13 @@
         <v>6.2</v>
       </c>
       <c r="D2">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="E2">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="F2">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1818,13 +1818,13 @@
         <v>0.3</v>
       </c>
       <c r="D3">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E3">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F3">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="G3">
         <v>2.5</v>
@@ -1847,10 +1847,10 @@
         <v>1.4</v>
       </c>
       <c r="F4">
-        <v>96.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G4">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2013,7 +2013,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2021,10 +2021,10 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2032,10 +2032,10 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C5">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2043,10 +2043,10 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C6">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2054,10 +2054,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C7">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>
@@ -2203,7 +2203,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2211,7 +2211,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2219,7 +2219,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -2248,7 +2248,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>931</v>
+        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2256,10 +2256,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2267,10 +2267,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C4">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2278,7 +2278,7 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>931</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -2316,7 +2316,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -2333,7 +2333,7 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -2350,7 +2350,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2364,10 +2364,10 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>33.6</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -2383,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
@@ -2408,10 +2408,10 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2444,13 +2444,16 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2458,13 +2461,13 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>372</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2472,38 +2475,41 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>367</v>
+        <v>67</v>
       </c>
       <c r="D7">
-        <v>83.2</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="D9">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2511,52 +2517,13 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="D10">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>62</v>
-      </c>
-      <c r="D11">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12">
-        <v>246</v>
-      </c>
-      <c r="D12">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>1.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2591,10 +2558,10 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2">
-        <v>87.7</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2622,7 +2589,7 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2647,10 +2614,10 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D6">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2661,10 +2628,10 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2678,7 +2645,7 @@
         <v>80</v>
       </c>
       <c r="D8">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2689,10 +2656,10 @@
         <v>24</v>
       </c>
       <c r="C9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2703,10 +2670,10 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D10">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
     </row>
   </sheetData>
@@ -2775,7 +2742,7 @@
         <v>47</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -2784,7 +2751,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2812,13 +2779,13 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D6">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E6">
-        <v>777</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2829,13 +2796,13 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2843,16 +2810,16 @@
         <v>44</v>
       </c>
       <c r="B8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D8">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E8">
-        <v>931</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -2912,13 +2879,13 @@
         <v>47</v>
       </c>
       <c r="B4">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="C4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2940,10 +2907,10 @@
         <v>49</v>
       </c>
       <c r="B6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="C6">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>54.1</v>
@@ -2957,10 +2924,10 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="D7">
-        <v>38.5</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
